--- a/data/trans_dic/P02E$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 17,84</t>
+          <t>2,18; 19,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,52</t>
+          <t>0,0; 15,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 13,79</t>
+          <t>1,65; 14,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,18</t>
+          <t>1,83; 11,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 24,69</t>
+          <t>9,73; 25,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 9,16</t>
+          <t>1,06; 9,21</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,43; 10,58</t>
+          <t>2,67; 10,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,14; 19,34</t>
+          <t>7,93; 19,07</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 20,39</t>
+          <t>9,89; 21,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,6; 10,15</t>
+          <t>3,68; 10,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 8,73</t>
+          <t>2,25; 9,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,78</t>
+          <t>6,41; 13,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,62</t>
+          <t>5,2; 10,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,92; 12,77</t>
+          <t>5,97; 12,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,72; 14,32</t>
+          <t>8,57; 14,09</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,32; 9,27</t>
+          <t>5,24; 9,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,75</t>
+          <t>5,08; 9,73</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,87; 10,11</t>
+          <t>3,89; 9,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,41; 7,94</t>
+          <t>3,1; 7,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,61; 8,72</t>
+          <t>3,55; 9,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,12</t>
+          <t>2,23; 6,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,95</t>
+          <t>2,54; 5,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,44; 12,03</t>
+          <t>6,33; 12,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,56</t>
+          <t>3,34; 6,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,76</t>
+          <t>3,3; 5,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,85; 9,75</t>
+          <t>5,79; 9,6</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,53</t>
+          <t>0,94; 8,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,59</t>
+          <t>0,88; 5,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,13</t>
+          <t>2,06; 9,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 6,29</t>
+          <t>0,69; 6,61</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,25</t>
+          <t>1,66; 6,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,45</t>
+          <t>1,78; 8,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,64</t>
+          <t>1,24; 5,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,88</t>
+          <t>1,72; 4,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,67</t>
+          <t>2,51; 7,47</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,2</t>
+          <t>0,0; 32,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,89</t>
+          <t>0,0; 15,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,13</t>
+          <t>0,0; 13,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,83</t>
+          <t>0,0; 12,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,78</t>
+          <t>1,06; 10,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 23,38</t>
+          <t>5,31; 23,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,98</t>
+          <t>1,24; 12,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,53</t>
+          <t>1,47; 8,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,32; 15,0</t>
+          <t>3,41; 14,94</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,04</t>
+          <t>0,0; 24,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,32</t>
+          <t>0,0; 24,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,79</t>
+          <t>0,0; 29,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,38</t>
+          <t>0,0; 11,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 16,66</t>
+          <t>1,96; 15,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 14,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 11,27</t>
+          <t>1,33; 11,7</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,43; 12,68</t>
+          <t>1,45; 13,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,09</t>
+          <t>1,68; 15,25</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,04; 44,99</t>
+          <t>5,36; 45,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,61; 63,38</t>
+          <t>7,63; 64,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 50,22</t>
+          <t>13,39; 54,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,81; 32,29</t>
+          <t>7,71; 33,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,44; 41,28</t>
+          <t>13,49; 45,62</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,06; 45,07</t>
+          <t>15,42; 44,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,98; 35,02</t>
+          <t>11,18; 34,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,0; 35,26</t>
+          <t>10,37; 34,23</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,39</t>
+          <t>6,35; 10,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,81</t>
+          <t>3,87; 6,71</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,61; 6,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,68</t>
+          <t>4,85; 7,73</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,66</t>
+          <t>4,17; 6,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,36</t>
+          <t>7,81; 11,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,26</t>
+          <t>5,69; 8,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,34</t>
+          <t>4,36; 6,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,09</t>
+          <t>6,54; 9,16</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1909</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>915; 7316</t>
+          <t>895; 7986</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6327</t>
+          <t>0; 6333</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>811; 6971</t>
+          <t>836; 7423</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1864; 11358</t>
+          <t>1856; 11722</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8823; 22190</t>
+          <t>8742; 22810</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>843; 7385</t>
+          <t>855; 7425</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3468; 15084</t>
+          <t>3815; 15459</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10633; 25267</t>
+          <t>10360; 24906</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15564; 34013</t>
+          <t>16494; 36000</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7708; 21746</t>
+          <t>7878; 21756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3866; 15134</t>
+          <t>3899; 15597</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18925; 38719</t>
+          <t>19411; 39446</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20309; 41459</t>
+          <t>20298; 41673</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17365; 37455</t>
+          <t>17516; 36332</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40978; 67274</t>
+          <t>40236; 66203</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32180; 56093</t>
+          <t>31689; 57141</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23598; 45523</t>
+          <t>23719; 45432</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10467; 27344</t>
+          <t>10527; 25381</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14145; 32924</t>
+          <t>12858; 31717</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11244; 27185</t>
+          <t>11070; 28888</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8948; 24016</t>
+          <t>8731; 23669</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14531; 34174</t>
+          <t>14555; 32213</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26252; 49013</t>
+          <t>25787; 49693</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21979; 43491</t>
+          <t>22122; 44259</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>31497; 56935</t>
+          <t>32598; 58774</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>42037; 70133</t>
+          <t>41667; 69004</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1050; 9423</t>
+          <t>1039; 9091</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1963; 12796</t>
+          <t>2009; 11632</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3225; 14316</t>
+          <t>3236; 14654</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>852; 7597</t>
+          <t>836; 7984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4359; 16356</t>
+          <t>4331; 16446</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3208; 15399</t>
+          <t>3245; 15911</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2891; 13039</t>
+          <t>2859; 13761</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8330; 23906</t>
+          <t>8422; 23879</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9322; 26003</t>
+          <t>8497; 25323</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5421</t>
+          <t>0; 5794</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7317</t>
+          <t>0; 7650</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5685</t>
+          <t>0; 5316</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 9938</t>
+          <t>0; 8409</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1118; 9832</t>
+          <t>1067; 10520</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2592; 13277</t>
+          <t>3014; 13431</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1013; 11030</t>
+          <t>1054; 10512</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2224; 12775</t>
+          <t>2207; 13289</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3222; 14553</t>
+          <t>3309; 14496</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4084</t>
+          <t>0; 5520</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6116</t>
+          <t>0; 6201</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 6279</t>
+          <t>0; 5452</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>943; 7880</t>
+          <t>927; 7456</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4433</t>
+          <t>0; 5171</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>800; 6887</t>
+          <t>814; 7151</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>992; 8823</t>
+          <t>1009; 9686</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>961; 8129</t>
+          <t>967; 8797</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>817; 7288</t>
+          <t>868; 7387</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1138; 9474</t>
+          <t>1140; 9611</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1570</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3418; 12770</t>
+          <t>3406; 13800</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3222; 13312</t>
+          <t>3180; 13924</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6035; 18533</t>
+          <t>6059; 20483</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6269; 18762</t>
+          <t>6420; 18625</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5608; 19672</t>
+          <t>6282; 19404</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5736; 20222</t>
+          <t>5947; 19629</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38959; 65075</t>
+          <t>39746; 66857</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>37619; 67032</t>
+          <t>38149; 66076</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27861; 51102</t>
+          <t>27325; 52759</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46801; 77212</t>
+          <t>48783; 77764</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63709; 100977</t>
+          <t>63294; 98066</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>85700; 126184</t>
+          <t>86790; 125425</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>93071; 134732</t>
+          <t>92870; 134030</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>110604; 158601</t>
+          <t>109007; 156063</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>121619; 169745</t>
+          <t>122174; 171046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Edad-trans_dic.xlsx
@@ -683,42 +683,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,18; 19,48</t>
+          <t>2,16; 17,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,54</t>
+          <t>0,0; 16,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 14,68</t>
+          <t>1,69; 14,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 11,53</t>
+          <t>1,83; 10,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 25,38</t>
+          <t>9,84; 24,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,21</t>
+          <t>1,05; 9,86</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,84</t>
+          <t>2,65; 10,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,93; 19,07</t>
+          <t>8,1; 18,84</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,89; 21,58</t>
+          <t>9,64; 20,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,15</t>
+          <t>3,69; 10,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 9,0</t>
+          <t>2,16; 8,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,41; 13,02</t>
+          <t>6,28; 12,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,2; 10,67</t>
+          <t>5,19; 10,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,97; 12,38</t>
+          <t>5,84; 12,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,57; 14,09</t>
+          <t>8,59; 14,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,45</t>
+          <t>5,2; 9,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,73</t>
+          <t>5,11; 9,88</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,38</t>
+          <t>3,89; 9,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,65</t>
+          <t>3,32; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 9,27</t>
+          <t>3,68; 9,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 6,04</t>
+          <t>2,24; 6,23</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,61</t>
+          <t>2,43; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,33; 12,2</t>
+          <t>6,31; 12,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,68</t>
+          <t>3,4; 6,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,95</t>
+          <t>3,23; 5,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,6</t>
+          <t>5,91; 9,75</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 8,23</t>
+          <t>0,95; 9,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,09</t>
+          <t>1,05; 5,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,34</t>
+          <t>2,01; 8,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,61</t>
+          <t>0,7; 7,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 6,29</t>
+          <t>1,31; 6,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,73</t>
+          <t>2,14; 9,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,95</t>
+          <t>1,26; 6,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,87</t>
+          <t>1,73; 4,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,47</t>
+          <t>2,73; 7,68</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,28</t>
+          <t>0,0; 32,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,57</t>
+          <t>0,0; 15,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,21</t>
+          <t>0,0; 13,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,55</t>
+          <t>0,0; 12,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,06; 10,46</t>
+          <t>1,11; 10,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 23,65</t>
+          <t>4,01; 22,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 12,37</t>
+          <t>1,19; 12,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 8,88</t>
+          <t>1,5; 8,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 14,94</t>
+          <t>3,27; 14,44</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,73</t>
+          <t>0,0; 24,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,76</t>
+          <t>0,0; 18,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,19</t>
+          <t>0,0; 29,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,62</t>
+          <t>0,0; 12,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 15,77</t>
+          <t>1,98; 17,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 11,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,7</t>
+          <t>1,32; 11,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,92</t>
+          <t>1,38; 12,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 15,25</t>
+          <t>1,68; 13,83</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,36; 45,61</t>
+          <t>5,34; 46,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,63; 64,29</t>
+          <t>7,65; 65,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1353,32 +1353,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,39; 54,27</t>
+          <t>13,53; 50,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 33,77</t>
+          <t>8,02; 32,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,49; 45,62</t>
+          <t>13,85; 43,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,42; 44,74</t>
+          <t>15,97; 43,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,18; 34,54</t>
+          <t>10,09; 34,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>10,37; 34,23</t>
+          <t>10,89; 35,56</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,68</t>
+          <t>6,14; 10,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,71</t>
+          <t>3,9; 6,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,97</t>
+          <t>3,73; 6,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,73</t>
+          <t>4,87; 7,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,46</t>
+          <t>4,21; 6,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,29</t>
+          <t>7,65; 11,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,21</t>
+          <t>5,68; 8,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,24</t>
+          <t>4,44; 6,25</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,16</t>
+          <t>6,58; 8,95</t>
         </is>
       </c>
     </row>
@@ -1755,42 +1755,42 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>895; 7986</t>
+          <t>886; 7309</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 6333</t>
+          <t>0; 6563</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>836; 7423</t>
+          <t>852; 7425</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1856; 11722</t>
+          <t>1857; 10788</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8742; 22810</t>
+          <t>8845; 22284</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>855; 7425</t>
+          <t>847; 7948</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3815; 15459</t>
+          <t>3777; 14927</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10360; 24906</t>
+          <t>10587; 24612</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16494; 36000</t>
+          <t>16076; 34293</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7878; 21756</t>
+          <t>7908; 22582</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3899; 15597</t>
+          <t>3749; 14913</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19411; 39446</t>
+          <t>19018; 39069</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20298; 41673</t>
+          <t>20285; 41382</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17516; 36332</t>
+          <t>17123; 36934</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40236; 66203</t>
+          <t>40372; 66676</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>31689; 57141</t>
+          <t>31458; 56834</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23719; 45432</t>
+          <t>23831; 46107</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10527; 25381</t>
+          <t>10520; 25026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12858; 31717</t>
+          <t>13752; 30818</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11070; 28888</t>
+          <t>11489; 28312</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8731; 23669</t>
+          <t>8793; 24427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14555; 32213</t>
+          <t>13974; 33616</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>25787; 49693</t>
+          <t>25703; 49016</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22122; 44259</t>
+          <t>22519; 43996</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32598; 58774</t>
+          <t>31881; 58338</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>41667; 69004</t>
+          <t>42511; 70128</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1039; 9091</t>
+          <t>1053; 10395</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2009; 11632</t>
+          <t>2408; 12122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3236; 14654</t>
+          <t>3159; 13917</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>836; 7984</t>
+          <t>844; 8552</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4331; 16446</t>
+          <t>3438; 16419</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3245; 15911</t>
+          <t>3893; 16571</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2859; 13761</t>
+          <t>2916; 13954</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8422; 23879</t>
+          <t>8481; 23754</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8497; 25323</t>
+          <t>9243; 26035</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5794</t>
+          <t>0; 5771</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7650</t>
+          <t>0; 7447</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5316</t>
+          <t>0; 5244</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 8409</t>
+          <t>0; 8184</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1067; 10520</t>
+          <t>1117; 10455</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3014; 13431</t>
+          <t>2274; 12629</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1054; 10512</t>
+          <t>1012; 10517</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2207; 13289</t>
+          <t>2245; 12852</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3309; 14496</t>
+          <t>3176; 14005</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3525</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 5520</t>
+          <t>0; 4067</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6201</t>
+          <t>0; 6244</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5452</t>
+          <t>0; 5740</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>927; 7456</t>
+          <t>935; 8098</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5171</t>
+          <t>0; 4367</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>814; 7151</t>
+          <t>805; 6998</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1009; 9686</t>
+          <t>960; 8911</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>967; 8797</t>
+          <t>967; 7979</t>
         </is>
       </c>
     </row>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>868; 7387</t>
+          <t>864; 7513</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1140; 9611</t>
+          <t>1144; 9797</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -2743,32 +2743,32 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3406; 13800</t>
+          <t>3442; 12777</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3180; 13924</t>
+          <t>3306; 13309</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6059; 20483</t>
+          <t>6218; 19328</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6420; 18625</t>
+          <t>6650; 18233</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>6282; 19404</t>
+          <t>5669; 19140</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5947; 19629</t>
+          <t>6245; 20392</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39746; 66857</t>
+          <t>38436; 66471</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>38149; 66076</t>
+          <t>38440; 67796</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>27325; 52759</t>
+          <t>28249; 52097</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>48783; 77764</t>
+          <t>48958; 79429</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>63294; 98066</t>
+          <t>63874; 100401</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>86790; 125425</t>
+          <t>85011; 125404</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92870; 134030</t>
+          <t>92771; 134876</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>109007; 156063</t>
+          <t>111033; 156376</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>122174; 171046</t>
+          <t>122813; 167237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
